--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487534_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487534_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.232100000000001</v>
+        <v>7.7185</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0099</v>
+        <v>6.1998</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7778</v>
+        <v>1.5188</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9173</v>
+        <v>6.3372</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3507</v>
+        <v>3.6187</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5665</v>
+        <v>2.7186</v>
       </c>
       <c r="J2" t="n">
-        <v>4.585</v>
+        <v>6.8508</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6402</v>
+        <v>4.0218</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9447</v>
+        <v>2.8291</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6677</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2895</v>
+        <v>-0.4031</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3782</v>
+        <v>-0.1105</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9792</v>
+        <v>1.5668</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1751</v>
+        <v>-0.1958</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1543</v>
+        <v>1.7626</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0614</v>
+        <v>0.3652</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3419</v>
+        <v>-0.4552</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7195</v>
+        <v>0.8205</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2742</v>
+        <v>-0.5507</v>
       </c>
       <c r="W2" t="n">
-        <v>4.2581</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.9839</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2115</v>
+        <v>6.4168</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5857</v>
+        <v>8.167899999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6257</v>
+        <v>-1.7511</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3372</v>
+        <v>2.9173</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6187</v>
+        <v>1.3507</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7186</v>
+        <v>1.5665</v>
       </c>
       <c r="J3" t="n">
-        <v>6.8508</v>
+        <v>4.585</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0218</v>
+        <v>2.6402</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8291</v>
+        <v>1.9447</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-1.6677</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4031</v>
+        <v>-1.2895</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1105</v>
+        <v>-0.3782</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1958</v>
+        <v>-1.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7626</v>
+        <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1419</v>
+        <v>1.2461</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0692</v>
+        <v>0.4999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9274</v>
+        <v>0.7462</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5507</v>
+        <v>1.2742</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>4.2581</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5507</v>
+        <v>-2.9839</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6984</v>
+        <v>5.7355</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8068</v>
+        <v>5.5231</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1083</v>
+        <v>0.2124</v>
       </c>
       <c r="G4" t="n">
         <v>5.2088</v>
@@ -766,13 +766,13 @@
         <v>2.1543</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7478</v>
+        <v>0.2894</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4256</v>
+        <v>-0.7093</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.9987</v>
       </c>
       <c r="V4" t="n">
         <v>1.2166</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7825</v>
+        <v>3.686</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1258</v>
+        <v>1.8421</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6568</v>
+        <v>1.8439</v>
       </c>
       <c r="G5" t="n">
         <v>0.2809</v>
@@ -844,13 +844,13 @@
         <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5397999999999999</v>
+        <v>0.3636</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4256</v>
+        <v>-0.7093</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8858</v>
+        <v>1.0729</v>
       </c>
       <c r="V5" t="n">
         <v>3.0415</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.933</v>
+        <v>1.6657</v>
       </c>
       <c r="E6" t="n">
         <v>2.3301</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.397</v>
+        <v>-0.6644</v>
       </c>
       <c r="G6" t="n">
         <v>1.7734</v>
@@ -922,13 +922,13 @@
         <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9857</v>
+        <v>0.7184</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2682</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2539</v>
+        <v>0.9866</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8260999999999999</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0645</v>
+        <v>-0.1355</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1599</v>
+        <v>0.9552</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2244</v>
+        <v>-1.0907</v>
       </c>
       <c r="G7" t="n">
         <v>1.0478</v>
@@ -1000,13 +1000,13 @@
         <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1838</v>
+        <v>0.1128</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0882</v>
+        <v>-0.1165</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0956</v>
+        <v>0.2292</v>
       </c>
       <c r="V7" t="n">
         <v>-1.492</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9177</v>
+        <v>-1.4073</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3854</v>
+        <v>-1.7947</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4677</v>
+        <v>0.3875</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1182</v>
@@ -1078,13 +1078,13 @@
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6705</v>
+        <v>0.181</v>
       </c>
       <c r="T8" t="n">
-        <v>0.207</v>
+        <v>-0.2023</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4635</v>
+        <v>0.3833</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6659</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3614</v>
+        <v>-2.3217</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4106</v>
+        <v>-0.1036</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9509</v>
+        <v>-2.2182</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7141</v>
@@ -1156,13 +1156,13 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.077</v>
+        <v>-0.0373</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6534</v>
+        <v>-0.3464</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5764</v>
+        <v>0.3091</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1578</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.233</v>
+        <v>-4.0772</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6834</v>
+        <v>-1.5811</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5496</v>
+        <v>-2.4961</v>
       </c>
       <c r="G10" t="n">
         <v>0.2242</v>
@@ -1234,13 +1234,13 @@
         <v>0.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4572</v>
+        <v>-0.3014</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3564</v>
+        <v>-0.2541</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1008</v>
+        <v>-0.0473</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4332</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>17.2809</v>
+        <v>17.2808</v>
       </c>
       <c r="E11" t="n">
         <v>21.5388</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.2578</v>
+        <v>-4.2579</v>
       </c>
       <c r="G11" t="n">
         <v>15.9573</v>
@@ -1312,10 +1312,10 @@
         <v>11.7507</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9377</v>
+        <v>2.9378</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.5613</v>
+        <v>-2.5614</v>
       </c>
       <c r="U11" t="n">
         <v>5.4992</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.1707</v>
+        <v>5.2405</v>
       </c>
       <c r="E12" t="n">
-        <v>6.4277</v>
+        <v>5.7114</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.257</v>
+        <v>-0.4708</v>
       </c>
       <c r="G12" t="n">
         <v>0.5268</v>
@@ -1390,13 +1390,13 @@
         <v>2.1543</v>
       </c>
       <c r="S12" t="n">
-        <v>0.819</v>
+        <v>-0.1112</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1347</v>
+        <v>-0.5817</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6844</v>
+        <v>0.4705</v>
       </c>
       <c r="V12" t="n">
         <v>3.6498</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0231</v>
+        <v>0.2324</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3454</v>
+        <v>-0.2431</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3686</v>
+        <v>0.4755</v>
       </c>
       <c r="G13" t="n">
         <v>0.3371</v>
@@ -1468,13 +1468,13 @@
         <v>0.9792</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3139</v>
+        <v>-0.1047</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1606</v>
+        <v>-0.0582</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1534</v>
+        <v>-0.0465</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.206</v>
+        <v>-0.1036</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6897</v>
+        <v>-0.5874</v>
       </c>
       <c r="F14" t="n">
         <v>0.4838</v>
@@ -1546,10 +1546,10 @@
         <v>0.1958</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.0076</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U14" t="n">
         <v>0.0241</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.3743</v>
       </c>
       <c r="E15" t="n">
         <v>0.9063</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4945</v>
+        <v>-1.2807</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9214</v>
@@ -1624,13 +1624,13 @@
         <v>0.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.5105</v>
       </c>
       <c r="T15" t="n">
         <v>-0.4576</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2668</v>
+        <v>-0.0529</v>
       </c>
       <c r="V15" t="n">
         <v>0.6659</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8537</v>
+        <v>-1.0629</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1186</v>
+        <v>5.0162</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.9722</v>
+        <v>-6.0791</v>
       </c>
       <c r="G16" t="n">
         <v>2.2168</v>
@@ -1702,13 +1702,13 @@
         <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1069</v>
+        <v>-0.1023</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1911</v>
+        <v>-0.2935</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2981</v>
+        <v>0.1911</v>
       </c>
       <c r="V16" t="n">
         <v>-3.765</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1466</v>
+        <v>-1.601</v>
       </c>
       <c r="E17" t="n">
         <v>-0.7622</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3844</v>
+        <v>-0.8389</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8711</v>
@@ -1780,13 +1780,13 @@
         <v>0.5875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.137</v>
+        <v>-0.3174</v>
       </c>
       <c r="T17" t="n">
         <v>-0.7722</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9092</v>
+        <v>0.4548</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1982</v>
+        <v>-1.9889</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2844</v>
+        <v>0.3867</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4825</v>
+        <v>-2.3756</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5808</v>
@@ -1858,13 +1858,13 @@
         <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2257</v>
+        <v>-0.0165</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.594</v>
+        <v>-0.4917</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3683</v>
+        <v>0.4752</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7763</v>
+        <v>-3.2555</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1965</v>
+        <v>-0.8895</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5799</v>
+        <v>-2.366</v>
       </c>
       <c r="G19" t="n">
         <v>-2.577</v>
@@ -1936,13 +1936,13 @@
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1578</v>
+        <v>-0.637</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.188</v>
+        <v>-0.881</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0302</v>
+        <v>0.2441</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2166</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.3552</v>
+        <v>-6.618</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.186</v>
+        <v>-4.2884</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1692</v>
+        <v>-2.3296</v>
       </c>
       <c r="G20" t="n">
         <v>-7.0187</v>
@@ -2014,13 +2014,13 @@
         <v>1.9585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1246</v>
+        <v>-0.3873</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8446</v>
+        <v>-0.9469</v>
       </c>
       <c r="U20" t="n">
-        <v>0.72</v>
+        <v>0.5596</v>
       </c>
       <c r="V20" t="n">
         <v>1.7673</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.3505</v>
+        <v>-7.7494</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2993</v>
+        <v>-0.9923</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.0512</v>
+        <v>-6.7572</v>
       </c>
       <c r="G21" t="n">
         <v>-5.0751</v>
@@ -2092,13 +2092,13 @@
         <v>1.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3596</v>
+        <v>-0.7585</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3068</v>
+        <v>-0.9998</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0528</v>
+        <v>0.2413</v>
       </c>
       <c r="V21" t="n">
         <v>0.8260999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-17.2809</v>
+        <v>-17.2807</v>
       </c>
       <c r="E22" t="n">
-        <v>4.2579</v>
+        <v>4.257700000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-21.5385</v>
+        <v>-21.5386</v>
       </c>
       <c r="G22" t="n">
         <v>-15.9572</v>
@@ -2170,10 +2170,10 @@
         <v>10.7715</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.9377</v>
+        <v>-2.937799999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-5.499000000000001</v>
+        <v>-5.4991</v>
       </c>
       <c r="U22" t="n">
         <v>2.5613</v>
